--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46255.64822379629</v>
+        <v>46280.170120891205</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>107</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46255.648448541666</v>
+        <v>46280.17012271991</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -526,6 +526,9 @@
     <t>Ingenieria y diseño:,Check Planos 4388</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1217690861929361</t>
   </si>
   <si>
@@ -758,9 +761,6 @@
   </si>
   <si>
     <t>Logistica:,Embalaje 4388</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217691240750948</t>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46255.64947474537</v>
+        <v>46281.1637093287</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -3916,8 +3916,8 @@
       <c r="S46" s="6">
         <v>0</v>
       </c>
-      <c r="T46" s="7" t="s">
-        <v>51</v>
+      <c r="T46" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="U46" s="11" t="s">
         <v>74</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46254.64673040509</v>
@@ -3965,10 +3965,10 @@
         <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="9">
         <v>46289</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46254.64674159722</v>
@@ -3998,16 +3998,16 @@
         <v>46255.6495339699</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46339</v>
@@ -4028,10 +4028,10 @@
         <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46339</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46254.646754699075</v>
@@ -4061,7 +4061,7 @@
         <v>46255.636225775466</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4085,7 +4085,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46254.64675688658</v>
@@ -4108,16 +4108,16 @@
         <v>46255.649623310186</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46310</v>
@@ -4135,13 +4135,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>127</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46311</v>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46254.64676135417</v>
@@ -4171,7 +4171,7 @@
         <v>46255.649733136575</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4198,13 +4198,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9">
         <v>46315</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46254.6467652662</v>
@@ -4234,16 +4234,16 @@
         <v>46255.64961998843</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I52" s="5">
         <v>46310</v>
@@ -4261,13 +4261,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46311</v>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46254.6467686574</v>
@@ -4297,7 +4297,7 @@
         <v>46255.64972939815</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4324,13 +4324,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="9">
         <v>46315</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46254.6467727662</v>
@@ -4360,16 +4360,16 @@
         <v>46255.649616435185</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I54" s="5">
         <v>46310</v>
@@ -4387,13 +4387,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46311</v>
@@ -4413,7 +4413,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46254.64677601852</v>
@@ -4423,7 +4423,7 @@
         <v>46255.64972537037</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4450,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="9">
         <v>46315</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46254.646778877315</v>
@@ -4486,7 +4486,7 @@
         <v>46255.63788684028</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4510,7 +4510,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46254.64678087963</v>
@@ -4533,16 +4533,16 @@
         <v>46255.64983976852</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I57" s="9">
         <v>46316</v>
@@ -4560,13 +4560,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q57" s="9">
         <v>46318</v>
@@ -4586,7 +4586,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46254.64678571759</v>
@@ -4596,16 +4596,16 @@
         <v>46255.64983620371</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I58" s="5">
         <v>46321</v>
@@ -4623,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q58" s="5">
         <v>46325</v>
@@ -4649,7 +4649,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
         <v>46254.6467994213</v>
@@ -4659,16 +4659,16 @@
         <v>46260.57751050926</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I59" s="9">
         <v>46328</v>
@@ -4686,13 +4686,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="9">
         <v>46328</v>
@@ -4712,7 +4712,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46254.646810833336</v>
@@ -4722,7 +4722,7 @@
         <v>46255.63928070602</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -4746,7 +4746,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46254.64681284722</v>
@@ -4769,16 +4769,16 @@
         <v>46266.17605825231</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I61" s="9">
         <v>46262</v>
@@ -4796,13 +4796,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>63</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q61" s="9">
         <v>46265</v>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46254.646816990746</v>
@@ -4832,16 +4832,16 @@
         <v>46255.64996159722</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I62" s="5">
         <v>46302</v>
@@ -4859,13 +4859,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q62" s="5">
         <v>46303</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46254.64682097222</v>
@@ -4895,16 +4895,16 @@
         <v>46255.64995738426</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I63" s="9">
         <v>46325</v>
@@ -4922,13 +4922,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q63" s="9">
         <v>46325</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46254.64692375</v>
@@ -4958,16 +4958,16 @@
         <v>46255.64995386574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I64" s="5">
         <v>46335</v>
@@ -4985,7 +4985,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>104</v>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46254.646927407404</v>
@@ -5021,7 +5021,7 @@
         <v>46255.64360596065</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5045,7 +5045,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5058,7 +5058,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46254.64693065972</v>
@@ -5068,7 +5068,7 @@
         <v>46255.65006753472</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5095,13 +5095,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q66" s="5">
         <v>46335</v>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B67" s="9">
         <v>46254.646966782406</v>
@@ -5131,7 +5131,7 @@
         <v>46255.65006378472</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5158,13 +5158,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q67" s="9">
         <v>46336</v>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46254.6469462963</v>
@@ -5194,7 +5194,7 @@
         <v>46255.6500599537</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5219,13 +5219,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q68" s="5">
         <v>46337</v>
@@ -5245,7 +5245,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B69" s="9">
         <v>46254.64699303241</v>
@@ -5255,7 +5255,7 @@
         <v>46255.65005642361</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5282,13 +5282,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q69" s="9">
         <v>46338</v>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46254.647011319445</v>
@@ -5318,7 +5318,7 @@
         <v>46255.65005247685</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5345,13 +5345,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q70" s="5">
         <v>46342</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B71" s="9">
         <v>46254.64706888889</v>
@@ -5381,7 +5381,7 @@
         <v>46255.644517175926</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5405,7 +5405,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5418,7 +5418,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B72" s="5">
         <v>46254.6470725463</v>
@@ -5428,16 +5428,16 @@
         <v>46275.14170949074</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I72" s="5">
         <v>46343</v>
@@ -5455,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q72" s="5">
         <v>46282</v>
@@ -5473,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="12" t="s">
-        <v>249</v>
+        <v>171</v>
       </c>
       <c r="U72" s="11" t="s">
         <v>74</v>
@@ -5518,10 +5518,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>252</v>
@@ -5560,10 +5560,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I74" s="5">
         <v>46345</v>
@@ -5581,7 +5581,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>251</v>
@@ -5623,10 +5623,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I75" s="9">
         <v>46346</v>
@@ -5644,7 +5644,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>254</v>

--- a/data/50001587 -  usach.xlsx
+++ b/data/50001587 -  usach.xlsx
@@ -3932,7 +3932,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46255.649470578704</v>
+        <v>46282.12922685185</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>84</v>
@@ -3979,8 +3979,8 @@
       <c r="S47" s="10">
         <v>0</v>
       </c>
-      <c r="T47" s="7" t="s">
-        <v>51</v>
+      <c r="T47" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="U47" s="11" t="s">
         <v>74</v>
